--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>80174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R14" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,45 +1996,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>80174</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R15" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1221,19 +1221,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1328,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
         <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>128980661</v>
       </c>
       <c r="B16" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B7" t="n">
         <v>57723</v>
@@ -1221,19 +1221,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1328,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1813,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R15" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128979800</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594408</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1328,19 +1323,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128979800</v>
+        <v>128980218</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,27 +1410,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594408</v>
+        <v>594386</v>
       </c>
       <c r="R9" t="n">
-        <v>6925628</v>
+        <v>6925740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R11" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R12" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,45 +797,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B3" t="n">
-        <v>91491</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R3" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R4" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979800</v>
+        <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594408</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>6925628</v>
+        <v>6925555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1323,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128980218</v>
+        <v>128979800</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,27 +1415,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594386</v>
+        <v>594408</v>
       </c>
       <c r="R9" t="n">
-        <v>6925740</v>
+        <v>6925628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R11" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R12" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980636</v>
+        <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,34 +2007,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594536</v>
+        <v>594424</v>
       </c>
       <c r="R15" t="n">
-        <v>6925604</v>
+        <v>6925596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128980323</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128980218</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>128979800</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>128979329</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>128980661</v>
       </c>
       <c r="B16" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128979699</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>128980610</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B7" t="n">
         <v>57725</v>
@@ -1221,19 +1221,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57725</v>
@@ -1328,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,45 +1899,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B14" t="n">
-        <v>80179</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R14" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1970,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R15" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,50 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>91506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R3" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R4" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
         <v>128979800</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>128979329</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,45 +1802,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80179</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,39 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R14" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1980,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,32 +2006,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R15" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>128980661</v>
       </c>
       <c r="B16" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128979699</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>128980610</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,45 +797,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B3" t="n">
-        <v>91506</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R3" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R4" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128979800</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594408</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1328,19 +1323,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128979800</v>
+        <v>128980218</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,27 +1410,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594408</v>
+        <v>594386</v>
       </c>
       <c r="R9" t="n">
-        <v>6925628</v>
+        <v>6925740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R14" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,45 +1996,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R15" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979800</v>
+        <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594408</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>6925628</v>
+        <v>6925555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1323,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128980218</v>
+        <v>128979800</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,27 +1415,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594386</v>
+        <v>594408</v>
       </c>
       <c r="R9" t="n">
-        <v>6925740</v>
+        <v>6925628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1813,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,32 +1909,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980671</v>
+        <v>128980636</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594528</v>
+        <v>594536</v>
       </c>
       <c r="R14" t="n">
-        <v>6925586</v>
+        <v>6925604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,50 +2006,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128979481</v>
+        <v>128980671</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594424</v>
+        <v>594528</v>
       </c>
       <c r="R15" t="n">
-        <v>6925596</v>
+        <v>6925586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,50 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R3" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R4" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128979800</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594408</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1328,19 +1323,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128979800</v>
+        <v>128980218</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1415,27 +1410,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594408</v>
+        <v>594386</v>
       </c>
       <c r="R9" t="n">
-        <v>6925628</v>
+        <v>6925740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1802,50 +1802,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980671</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594528</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,45 +1996,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R15" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980671</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594528</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925586</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R14" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980671</v>
+        <v>128980636</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594528</v>
+        <v>594536</v>
       </c>
       <c r="R14" t="n">
-        <v>6925586</v>
+        <v>6925604</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
         <v>128980661</v>
       </c>
       <c r="B16" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R11" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B12" t="n">
-        <v>80183</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R12" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1323,19 +1323,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1430,19 +1430,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R9" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80183</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R11" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R12" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,45 +1802,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,7 +1912,7 @@
         <v>128980636</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,50 +2006,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128979481</v>
+        <v>128980671</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594424</v>
+        <v>594528</v>
       </c>
       <c r="R15" t="n">
-        <v>6925596</v>
+        <v>6925586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,7 +2106,7 @@
         <v>128980661</v>
       </c>
       <c r="B16" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,45 +797,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B3" t="n">
-        <v>91509</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R3" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R4" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128979307</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1323,19 +1323,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594545</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1430,19 +1430,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R9" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,32 +1899,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1944,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R14" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,45 +1996,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R15" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2072,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,50 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R3" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +894,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B4" t="n">
-        <v>91513</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R4" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>128980000</v>
       </c>
       <c r="B5" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128980184</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979800</v>
+        <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,39 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594408</v>
+        <v>594545</v>
       </c>
       <c r="R7" t="n">
-        <v>6925628</v>
+        <v>6925555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128979307</v>
+        <v>128980218</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1323,19 +1328,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594545</v>
+        <v>594386</v>
       </c>
       <c r="R8" t="n">
-        <v>6925555</v>
+        <v>6925740</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128980218</v>
+        <v>128979800</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,27 +1415,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594386</v>
+        <v>594408</v>
       </c>
       <c r="R9" t="n">
-        <v>6925740</v>
+        <v>6925628</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R11" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R12" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1813,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1996,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,39 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R15" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -797,45 +797,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980342</v>
+        <v>128980323</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594461</v>
+        <v>594463</v>
       </c>
       <c r="R3" t="n">
-        <v>6925708</v>
+        <v>6925718</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R4" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1608,32 +1608,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979715</v>
+        <v>128979734</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594424</v>
+        <v>594440</v>
       </c>
       <c r="R11" t="n">
-        <v>6925596</v>
+        <v>6925661</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979734</v>
+        <v>128979715</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594440</v>
+        <v>594424</v>
       </c>
       <c r="R12" t="n">
-        <v>6925661</v>
+        <v>6925596</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128979481</v>
+        <v>128980636</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,39 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594424</v>
+        <v>594536</v>
       </c>
       <c r="R13" t="n">
-        <v>6925596</v>
+        <v>6925604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,45 +1899,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128980671</v>
+        <v>128979481</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>594528</v>
+        <v>594424</v>
       </c>
       <c r="R14" t="n">
-        <v>6925586</v>
+        <v>6925596</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1980,6 +1975,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,32 +2006,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980636</v>
+        <v>128980671</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594536</v>
+        <v>594528</v>
       </c>
       <c r="R15" t="n">
-        <v>6925604</v>
+        <v>6925586</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128980218</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128979481</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128979699</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -1193,7 +1193,7 @@
         <v>128979307</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128980218</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>128979481</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>128979699</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -675,70 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113283809</v>
+        <v>128980184</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stormyra, Lillström, Stöde, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594563</v>
+        <v>594375</v>
       </c>
       <c r="R2" t="n">
-        <v>6925649</v>
+        <v>6925716</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Forsberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Forsberg</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128980323</v>
+        <v>128980342</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594463</v>
+        <v>594461</v>
       </c>
       <c r="R3" t="n">
-        <v>6925718</v>
+        <v>6925708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128980342</v>
+        <v>128979734</v>
       </c>
       <c r="B4" t="n">
-        <v>91514</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594461</v>
+        <v>594440</v>
       </c>
       <c r="R4" t="n">
-        <v>6925708</v>
+        <v>6925661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128980000</v>
+        <v>128980636</v>
       </c>
       <c r="B5" t="n">
-        <v>97595</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594378</v>
+        <v>594536</v>
       </c>
       <c r="R5" t="n">
-        <v>6925672</v>
+        <v>6925604</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128980184</v>
+        <v>128980661</v>
       </c>
       <c r="B6" t="n">
-        <v>91550</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594375</v>
+        <v>594528</v>
       </c>
       <c r="R6" t="n">
-        <v>6925716</v>
+        <v>6925586</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128979307</v>
+        <v>128979715</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>80467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594545</v>
+        <v>594424</v>
       </c>
       <c r="R7" t="n">
-        <v>6925555</v>
+        <v>6925596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128980218</v>
+        <v>128980671</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>80467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>594386</v>
+        <v>594528</v>
       </c>
       <c r="R8" t="n">
-        <v>6925740</v>
+        <v>6925586</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,50 +1354,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128979800</v>
+        <v>128979329</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>594408</v>
+        <v>594551</v>
       </c>
       <c r="R9" t="n">
-        <v>6925628</v>
+        <v>6925564</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,14 +1456,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128979329</v>
+        <v>128980323</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1542,14 +1492,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>594551</v>
+        <v>594463</v>
       </c>
       <c r="R10" t="n">
-        <v>6925564</v>
+        <v>6925718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,45 +1558,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128979734</v>
+        <v>128980610</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>594440</v>
+        <v>594528</v>
       </c>
       <c r="R11" t="n">
-        <v>6925661</v>
+        <v>6925586</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,45 +1664,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128979715</v>
+        <v>128979307</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>594424</v>
+        <v>594545</v>
       </c>
       <c r="R12" t="n">
-        <v>6925596</v>
+        <v>6925555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1740,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1771,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128980636</v>
+        <v>128979481</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1782,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Lekmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>594536</v>
+        <v>594424</v>
       </c>
       <c r="R13" t="n">
-        <v>6925604</v>
+        <v>6925596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,6 +1847,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128979481</v>
+        <v>128979699</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,10 +1906,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1942,7 +1925,7 @@
         <v>594424</v>
       </c>
       <c r="R14" t="n">
-        <v>6925596</v>
+        <v>6925680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,11 +1958,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,45 +1984,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128980671</v>
+        <v>128980218</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>594528</v>
+        <v>594386</v>
       </c>
       <c r="R15" t="n">
-        <v>6925586</v>
+        <v>6925740</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2060,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2091,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128980661</v>
+        <v>113283809</v>
       </c>
       <c r="B16" t="n">
-        <v>80178</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,34 +2102,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flinthällan, Mpd</t>
+          <t>Stormyra, Lillström, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>594528</v>
+        <v>594563</v>
       </c>
       <c r="R16" t="n">
-        <v>6925586</v>
+        <v>6925649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,12 +2176,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,22 +2196,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Forsberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Hans Forsberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128979699</v>
+        <v>128979800</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,43 +2219,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lekmyran, Mpd</t>
+          <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>594424</v>
+        <v>594408</v>
       </c>
       <c r="R17" t="n">
-        <v>6925680</v>
+        <v>6925628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,54 +2310,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128980610</v>
+        <v>128980000</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flinthällan, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>594528</v>
+        <v>594378</v>
       </c>
       <c r="R18" t="n">
-        <v>6925586</v>
+        <v>6925672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 45572-2025 artfynd.xlsx
+++ b/artfynd/A 45572-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980342</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979715</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980671</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979329</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980323</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980610</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1768,6 +1823,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979307</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980218</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113283809</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128979800</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,8 +2489,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128980000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>